--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-frameworks-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-frameworks-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Tính năng AI dự báo là dạng Attractive (nếu chạy tốt) hoặc Indifferent (nếu chạy không chính xác, khách hàng không quan tâm lắm). Vì nỗ lực lớn nhưng giá trị chưa rõ ràng, BA cần tư vấn PO không đưa vào MVP để bảo vệ scope.</v>
       </c>
       <c r="F2" t="str">
-        <v>Attractive (Hấp dẫn) hoặc Indifferent (Thờ ơ) — cần đánh giá kỹ lưỡng, có thể đưa vào backlog nghiên cứu (Spike) thay vì làm ngay làm tăng rủi ro dự án — cân đối giá trị</v>
+        <v>One-dimensional (Tuyến tính) — khách hàng sẽ đánh giá chất lượng sản phẩm tăng dần theo số lượng thuật toán AI được code — tuyến tính hài lòng</v>
       </c>
       <c r="G2" t="str">
         <v>Must-be (Cơ bản) — bắt buộc phải phát triển ngay từ bản MVP đầu tiên để hệ thống hoạt động được — yêu cầu cốt lõi</v>
       </c>
       <c r="H2" t="str">
-        <v>One-dimensional (Tuyến tính) — khách hàng sẽ đánh giá chất lượng sản phẩm tăng dần theo số lượng thuật toán AI được code — tuyến tính hài lòng</v>
+        <v>Attractive (Hấp dẫn) hoặc Indifferent (Thờ ơ) — cần đánh giá kỹ lưỡng, có thể đưa vào backlog nghiên cứu (Spike) thay vì làm ngay làm tăng rủi ro dự án — cân đối giá trị</v>
       </c>
       <c r="I2" t="str">
         <v>Reverse (Ngược chiều) — tính năng này sẽ làm khách hàng cực kỳ ghét sản phẩm nếu hệ thống hoạt động chính xác — tác động tiêu cực</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Hoạt động hỗ trợ (Support Activities); đóng vai trò tối ưu hóa hiệu suất và giảm chi phí cho các hoạt động chính thông qua ứng dụng công nghệ thông tin — nâng cao năng lực nội tại</v>
       </c>
       <c r="G3" t="str">
-        <v>Hoạt động chính (Primary Activities); trực tiếp tham gia vào việc sản xuất và vận chuyển sản phẩm vật lý đến tay khách hàng — tạo ra sản phẩm</v>
+        <v>Hoạt động tiếp thị trực tuyến; chạy quảng cáo trên các nền tảng mạng xã hội lớn — thu hút khách hàng</v>
       </c>
       <c r="H3" t="str">
         <v>Hoạt động quản trị rủi ro pháp lý; ngăn chặn các cuộc tấn công bảo mật từ hacker bên ngoài — bảo mật hệ thống</v>
       </c>
       <c r="I3" t="str">
-        <v>Hoạt động tiếp thị trực tuyến; chạy quảng cáo trên các nền tảng mạng xã hội lớn — thu hút khách hàng</v>
+        <v>Hoạt động chính (Primary Activities); trực tiếp tham gia vào việc sản xuất và vận chuyển sản phẩm vật lý đến tay khách hàng — tạo ra sản phẩm</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>Nhóm High Power/Low Interest (ví dụ: Giám đốc tài chính hoặc Trưởng bộ phận an ninh thông tin) có quyền phủ quyết dự án. Nếu làm phiền họ quá nhiều bằng chi tiết nhỏ (Manage Closely) họ sẽ bực mình, nhưng nếu không giữ họ hài lòng (Keep Satisfied), họ có thể block dự án khi phát sinh vấn đề liên quan đến họ.</v>
       </c>
       <c r="F4" t="str">
-        <v>Keep Satisfied (Giữ cho họ hài lòng) bằng cách báo cáo các mốc tiến độ lớn một cách ngắn gọn, súc tích và tham vấn họ ở các quyết định quan trọng ảnh hưởng đến quyền lợi của họ — quản lý kỳ vọng khôn ngoan</v>
+        <v>Manage Closely (Quản lý chặt chẽ) bằng cách gửi email báo cáo chi tiết hàng ngày và bắt họ tham gia tất cả các cuộc họp Daily Scrum — làm phiền không cần thiết</v>
       </c>
       <c r="G4" t="str">
         <v>Monitor (Theo dõi sát sao) nhưng không cần cung cấp bất kỳ thông tin nào để tránh làm phiền họ — theo dõi thụ động</v>
       </c>
       <c r="H4" t="str">
-        <v>Manage Closely (Quản lý chặt chẽ) bằng cách gửi email báo cáo chi tiết hàng ngày và bắt họ tham gia tất cả các cuộc họp Daily Scrum — làm phiền không cần thiết</v>
+        <v>Bỏ qua hoàn toàn vì họ không quan tâm trực tiếp đến dự án nên sẽ không gây ảnh hưởng gì — chủ quan nguy hiểm</v>
       </c>
       <c r="I4" t="str">
-        <v>Bỏ qua hoàn toàn vì họ không quan tâm trực tiếp đến dự án nên sẽ không gây ảnh hưởng gì — chủ quan nguy hiểm</v>
+        <v>Keep Satisfied (Giữ cho họ hài lòng) bằng cách báo cáo các mốc tiến độ lớn một cách ngắn gọn, súc tích và tham vấn họ ở các quyết định quan trọng ảnh hưởng đến quyền lợi của họ — quản lý kỳ vọng khôn ngoan</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>Chọn lựa ngôn ngữ lập trình Java hay C# để viết API kết nối dữ liệu giữa các cửa hàng — lựa chọn công nghệ</v>
       </c>
       <c r="H5" t="str">
+        <v>Tìm kiếm nhà cung cấp máy chủ vật lý có giá thuê rẻ nhất trên thị trường — tối ưu chi phí phần cứng</v>
+      </c>
+      <c r="I5" t="str">
         <v>Tính toán số lượng nhân viên bán hàng tối đa cần tuyển dụng cho mỗi cửa hàng vật lý — quản lý nhân sự cửa hàng</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Tìm kiếm nhà cung cấp máy chủ vật lý có giá thuê rẻ nhất trên thị trường — tối ưu chi phí phần cứng</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -591,13 +591,13 @@
         <v>Phân tích trạng thái hiện tại, xác định trạng thái tương lai mong muốn, đánh giá rủi ro chiến lược và xác định phương án thay đổi (Change Strategy) — xác định lộ trình chuyển đổi</v>
       </c>
       <c r="G6" t="str">
+        <v>Thiết kế kiến trúc cơ sở dữ liệu vật lý và cài đặt hệ quản trị cơ sở dữ liệu PostgreSQL — thiết kế database</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Thương lượng mức giá chiết khấu phần trăm với nhà cung cấp dịch vụ máy chủ Cloud — thương thảo chi phí</v>
+      </c>
+      <c r="I6" t="str">
         <v>Viết toàn bộ kịch bản kiểm thử tích hợp API và chạy tự động trên môi trường Jenkins — kiểm thử tự động</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Thiết kế kiến trúc cơ sở dữ liệu vật lý và cài đặt hệ quản trị cơ sở dữ liệu PostgreSQL — thiết kế database</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Thương lượng mức giá chiết khấu phần trăm với nhà cung cấp dịch vụ máy chủ Cloud — thương thảo chi phí</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -623,13 +623,13 @@
         <v>Vì nó làm rõ ai là người chịu trách nhiệm giải trình cuối cùng (Accountable - chỉ có 1 người duy nhất), tránh tình trạng đùn đẩy trách nhiệm hoặc có quá nhiều người cùng đòi quyết định — phân định thẩm quyền rõ ràng</v>
       </c>
       <c r="G7" t="str">
-        <v>Vì RACI tự động hóa quy trình ký duyệt tài liệu điện tử thông qua các thuật toán mã hóa Blockchain — tự động hóa chữ ký</v>
+        <v>Vì nó loại bỏ hoàn toàn vai trò của giám đốc dự án ra khỏi quy trình kiểm soát tiến độ công việc — loại bỏ PM</v>
       </c>
       <c r="H7" t="str">
         <v>Vì nó bắt buộc tất cả các lập trình viên phải ký cam kết không được viết code sai so với đặc tả của BA — giảm thiểu bug code</v>
       </c>
       <c r="I7" t="str">
-        <v>Vì nó loại bỏ hoàn toàn vai trò của giám đốc dự án ra khỏi quy trình kiểm soát tiến độ công việc — loại bỏ PM</v>
+        <v>Vì RACI tự động hóa quy trình ký duyệt tài liệu điện tử thông qua các thuật toán mã hóa Blockchain — tự động hóa chữ ký</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -655,13 +655,13 @@
         <v>Dùng để thấu hiểu quan điểm của các bên liên quan về một hệ thống phức tạp; viết tắt của Customers, Actors, Transformation process, World view, Owners, Environmental constraints — phân tích góc nhìn hệ thống</v>
       </c>
       <c r="G8" t="str">
-        <v>Dùng để tính toán hiệu năng của hệ quản trị cơ sở dữ liệu quan hệ; viết tắt của Cache, Allocation, Transactions, Write-speed, Operations, Execution — chỉ số cơ sở dữ liệu</v>
+        <v>Dùng để lập lịch trình họp hàng tuần cho Scrum Team; viết tắt của Calendar, Agenda, Timebox, Weekly-goals, Outcomes, Evaluation — tổ chức cuộc họp</v>
       </c>
       <c r="H8" t="str">
         <v>Dùng để thiết kế giao diện đồ họa cho ứng dụng di động; viết tắt của Colors, Alignments, Typography, Width, Objects, Effects — quy tắc thiết kế giao diện</v>
       </c>
       <c r="I8" t="str">
-        <v>Dùng để lập lịch trình họp hàng tuần cho Scrum Team; viết tắt của Calendar, Agenda, Timebox, Weekly-goals, Outcomes, Evaluation — tổ chức cuộc họp</v>
+        <v>Dùng để tính toán hiệu năng của hệ quản trị cơ sở dữ liệu quan hệ; viết tắt của Cache, Allocation, Transactions, Write-speed, Operations, Execution — chỉ số cơ sở dữ liệu</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -687,13 +687,13 @@
         <v>Legal (Pháp lý); buộc thiết kế hệ thống phải có bước duyệt thủ công (Human-in-the-loop) đối với các hồ sơ bị AI đánh giá từ chối — ràng buộc pháp lý bắt buộc</v>
       </c>
       <c r="G9" t="str">
+        <v>Technological (Công nghệ); yêu cầu hệ thống phải sử dụng thuật toán học máy Deep Learning thay vì Random Forest — lựa chọn thuật toán</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Economic (Kinh tế); yêu cầu hệ thống phải tính phí giao dịch cao hơn đối với các hồ sơ bảo hiểm trực tuyến — điều chỉnh phí</v>
+      </c>
+      <c r="I9" t="str">
         <v>Social (Xã hội); yêu cầu hệ thống phải đổi giao diện sang màu vàng để tạo cảm giác thân thiện với người dùng — thiết kế thân thiện</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Technological (Công nghệ); yêu cầu hệ thống phải sử dụng thuật toán học máy Deep Learning thay vì Random Forest — lựa chọn thuật toán</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Economic (Kinh tế); yêu cầu hệ thống phải tính phí giao dịch cao hơn đối với các hồ sơ bảo hiểm trực tuyến — điều chỉnh phí</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>GAP không chỉ là con số chênh lệch hiệu năng, mà là khoảng trống về mặt năng lực hệ thống bao gồm: hạ tầng kỹ thuật, quy trình vận hành mới, và năng lực con người cần được bổ sung để đạt được trạng thái To-Be.</v>
       </c>
       <c r="F10" t="str">
-        <v>Sự thiếu hụt về hạ tầng phần cứng (cổng RFID, thẻ chip), sự thay đổi quy trình nghiệp vụ (không cần quét tay) và nhu cầu đào tạo nhân viên vận hành mới — các khoảng trống cần lấp đầy</v>
+        <v>Hiệu số thời gian chênh lệch là 4.9 giây trên mỗi sản phẩm được quét — chênh lệch thời gian</v>
       </c>
       <c r="G10" t="str">
-        <v>Hiệu số thời gian chênh lệch là 4.9 giây trên mỗi sản phẩm được quét — chênh lệch thời gian</v>
+        <v>Ngôn ngữ lập trình cần viết cho đầu đọc thẻ RFID để nó truyền dữ liệu về database — giải pháp kỹ thuật đọc RFID</v>
       </c>
       <c r="H10" t="str">
         <v>Tổng chi phí mua thiết bị RFID so với chi phí thuê nhân công quét mã vạch thủ công — chênh lệch tài chính</v>
       </c>
       <c r="I10" t="str">
-        <v>Ngôn ngữ lập trình cần viết cho đầu đọc thẻ RFID để nó truyền dữ liệu về database — giải pháp kỹ thuật đọc RFID</v>
+        <v>Sự thiếu hụt về hạ tầng phần cứng (cổng RFID, thẻ chip), sự thay đổi quy trình nghiệp vụ (không cần quét tay) và nhu cầu đào tạo nhân viên vận hành mới — các khoảng trống cần lấp đầy</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Triệu chứng (như nhân viên nhập liệu chậm) có thể do nhiều nguyên nhân gốc rễ (giao diện thiết kế tồi, thiếu phím tắt, hoặc hệ thống mạng chậm). Nếu BA đề xuất giải pháp sai nguyên nhân gốc, phần mềm xây xong sẽ vô dụng, gây lãng phí.</v>
       </c>
       <c r="F11" t="str">
+        <v>Vì khách hàng chỉ trả tiền cho dự án nếu BA chứng minh được lỗi hoàn toàn thuộc về hệ thống máy chủ cũ — phục vụ thanh toán</v>
+      </c>
+      <c r="G11" t="str">
         <v>Vì giải quyết triệu chứng chỉ mang tính tạm thời và vấn đề sẽ tiếp tục tái diễn; chỉ khi triệt tiêu nguyên nhân gốc rễ thì giải pháp phần mềm mới mang lại giá trị lâu dài — giải quyết triệt để</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Vì việc tìm nguyên nhân gốc rễ giúp lập trình viên viết code nhanh hơn mà không cần chạy kiểm thử hệ thống — tăng tốc độ code</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Vì khách hàng chỉ trả tiền cho dự án nếu BA chứng minh được lỗi hoàn toàn thuộc về hệ thống máy chủ cũ — phục vụ thanh toán</v>
       </c>
       <c r="I11" t="str">
         <v>Vì triệu chứng là yếu tố phi chức năng còn nguyên nhân gốc rễ luôn luôn là yêu cầu chức năng hệ thống — phân loại yêu cầu</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
